--- a/artfynd/A 40942-2019 artfynd.xlsx
+++ b/artfynd/A 40942-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40942-2019 artfynd.xlsx
+++ b/artfynd/A 40942-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,6 +1029,127 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123272267</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hulta, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499634</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506292</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40942-2019 artfynd.xlsx
+++ b/artfynd/A 40942-2019 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>123272267</v>
       </c>
       <c r="B5" t="n">
-        <v>56821</v>
+        <v>56824</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2019 artfynd.xlsx
+++ b/artfynd/A 40942-2019 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>123272267</v>
       </c>
       <c r="B5" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2019 artfynd.xlsx
+++ b/artfynd/A 40942-2019 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>123272267</v>
       </c>
       <c r="B5" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2019 artfynd.xlsx
+++ b/artfynd/A 40942-2019 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>123272267</v>
       </c>
       <c r="B5" t="n">
-        <v>56833</v>
+        <v>56834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
